--- a/code/output/model_output/apollo/battery/0_battery_model_combine_output.xlsx
+++ b/code/output/model_output/apollo/battery/0_battery_model_combine_output.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xnw17/Documents/GitHub/Conjoint_Survey_25/code/output/model_output/apollo/battery/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08A59855-3482-9949-8CDE-040DDC00FC71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16A45A9A-C437-E244-A71B-1C9489C29CCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="880" yWindow="1820" windowWidth="28880" windowHeight="15340" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="680" yWindow="660" windowWidth="28880" windowHeight="17440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="coef_fit" sheetId="1" r:id="rId1"/>
@@ -602,9 +602,6 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -658,17 +655,8 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="2" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -689,6 +677,18 @@
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="2" fontId="11" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3511,59 +3511,59 @@
   <sheetPr>
     <tabColor rgb="FFC00000"/>
   </sheetPr>
-  <dimension ref="A1:Y25"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="14.1640625" style="30" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" style="30"/>
-    <col min="3" max="3" width="10.83203125" style="31"/>
-    <col min="4" max="4" width="10.83203125" style="32"/>
-    <col min="5" max="5" width="27.83203125" style="33" customWidth="1"/>
-    <col min="6" max="15" width="10.83203125" style="30"/>
-    <col min="16" max="19" width="16.1640625" style="34" customWidth="1"/>
-    <col min="20" max="21" width="10.83203125" style="35"/>
-    <col min="22" max="22" width="19.83203125" style="35" customWidth="1"/>
+    <col min="1" max="1" width="14.1640625" style="29" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" style="29"/>
+    <col min="3" max="3" width="10.83203125" style="30"/>
+    <col min="4" max="4" width="10.83203125" style="31"/>
+    <col min="5" max="5" width="27.83203125" style="32" customWidth="1"/>
+    <col min="6" max="15" width="10.83203125" style="29"/>
+    <col min="16" max="19" width="16.1640625" style="33" customWidth="1"/>
+    <col min="20" max="21" width="10.83203125" style="34"/>
+    <col min="22" max="22" width="19.83203125" style="34" customWidth="1"/>
     <col min="23" max="23" width="10.83203125" style="4"/>
-    <col min="24" max="24" width="18.1640625" style="36" customWidth="1"/>
-    <col min="25" max="16384" width="10.83203125" style="30"/>
+    <col min="24" max="24" width="18.1640625" style="35" customWidth="1"/>
+    <col min="25" max="16384" width="10.83203125" style="29"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="16" customFormat="1" ht="41" customHeight="1">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:25" s="15" customFormat="1" ht="41" customHeight="1">
+      <c r="A1" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="15"/>
+      <c r="B1" s="14"/>
       <c r="C1" s="1"/>
       <c r="D1" s="2"/>
-      <c r="E1" s="16" t="s">
+      <c r="E1" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
+      <c r="J1" s="52"/>
+      <c r="K1" s="52"/>
       <c r="L1" s="11"/>
-      <c r="M1" s="13" t="s">
+      <c r="M1" s="52" t="s">
         <v>20</v>
       </c>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
-      <c r="P1" s="13"/>
-      <c r="Q1" s="13"/>
-      <c r="R1" s="13"/>
-      <c r="S1" s="13"/>
+      <c r="N1" s="52"/>
+      <c r="O1" s="52"/>
+      <c r="P1" s="52"/>
+      <c r="Q1" s="52"/>
+      <c r="R1" s="52"/>
+      <c r="S1" s="52"/>
       <c r="T1" s="3"/>
       <c r="U1" s="3"/>
       <c r="V1" s="3"/>
       <c r="W1" s="3"/>
-      <c r="X1" s="17"/>
-    </row>
-    <row r="2" spans="1:25" s="16" customFormat="1" ht="73" customHeight="1">
-      <c r="A2" s="16" t="s">
+      <c r="X1" s="16"/>
+    </row>
+    <row r="2" spans="1:25" s="15" customFormat="1" ht="73" customHeight="1">
+      <c r="A2" s="15" t="s">
         <v>22</v>
       </c>
       <c r="B2" s="3" t="s">
@@ -3594,8 +3594,8 @@
       <c r="K2" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="L2" s="18"/>
-      <c r="M2" s="16" t="s">
+      <c r="L2" s="17"/>
+      <c r="M2" s="15" t="s">
         <v>48</v>
       </c>
       <c r="N2" s="3" t="s">
@@ -3616,89 +3616,89 @@
       <c r="S2" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="T2" s="42" t="s">
+      <c r="T2" s="38" t="s">
         <v>49</v>
       </c>
-      <c r="U2" s="42" t="s">
+      <c r="U2" s="38" t="s">
         <v>50</v>
       </c>
-      <c r="V2" s="42" t="s">
+      <c r="V2" s="38" t="s">
         <v>51</v>
       </c>
-      <c r="W2" s="42" t="s">
+      <c r="W2" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="X2" s="19"/>
-    </row>
-    <row r="3" spans="1:25" s="20" customFormat="1" ht="61" customHeight="1">
-      <c r="B3" s="21"/>
-      <c r="C3" s="22"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="23"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="21" t="s">
+      <c r="X2" s="18"/>
+    </row>
+    <row r="3" spans="1:25" s="19" customFormat="1" ht="61" customHeight="1">
+      <c r="B3" s="20"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="H3" s="21" t="s">
+      <c r="H3" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="I3" s="21" t="s">
+      <c r="I3" s="20" t="s">
         <v>95</v>
       </c>
-      <c r="J3" s="21" t="s">
+      <c r="J3" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="K3" s="21" t="s">
+      <c r="K3" s="20" t="s">
         <v>97</v>
       </c>
-      <c r="L3" s="21"/>
-      <c r="M3" s="24">
+      <c r="L3" s="20"/>
+      <c r="M3" s="23">
         <v>10000</v>
       </c>
-      <c r="N3" s="21" t="s">
+      <c r="N3" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="O3" s="21" t="s">
+      <c r="O3" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="P3" s="22"/>
-      <c r="Q3" s="22"/>
-      <c r="R3" s="22"/>
-      <c r="S3" s="22"/>
-      <c r="T3" s="21"/>
-      <c r="U3" s="21"/>
-      <c r="V3" s="21"/>
-      <c r="W3" s="21"/>
-      <c r="X3" s="25"/>
-    </row>
-    <row r="4" spans="1:25" s="20" customFormat="1" ht="40" hidden="1" customHeight="1">
-      <c r="B4" s="21"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="21"/>
-      <c r="H4" s="21"/>
-      <c r="I4" s="21"/>
-      <c r="J4" s="21"/>
-      <c r="K4" s="21"/>
-      <c r="L4" s="21"/>
-      <c r="N4" s="21"/>
-      <c r="O4" s="21"/>
-      <c r="P4" s="22"/>
-      <c r="Q4" s="22"/>
-      <c r="R4" s="22"/>
-      <c r="S4" s="22"/>
-      <c r="T4" s="21"/>
-      <c r="U4" s="21"/>
-      <c r="V4" s="21"/>
-      <c r="W4" s="21"/>
-      <c r="X4" s="25"/>
-    </row>
-    <row r="5" spans="1:25" s="26" customFormat="1" ht="19" hidden="1" customHeight="1">
+      <c r="P3" s="21"/>
+      <c r="Q3" s="21"/>
+      <c r="R3" s="21"/>
+      <c r="S3" s="21"/>
+      <c r="T3" s="20"/>
+      <c r="U3" s="20"/>
+      <c r="V3" s="20"/>
+      <c r="W3" s="20"/>
+      <c r="X3" s="24"/>
+    </row>
+    <row r="4" spans="1:25" s="19" customFormat="1" ht="40" hidden="1" customHeight="1">
+      <c r="B4" s="20"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="20"/>
+      <c r="H4" s="20"/>
+      <c r="I4" s="20"/>
+      <c r="J4" s="20"/>
+      <c r="K4" s="20"/>
+      <c r="L4" s="20"/>
+      <c r="N4" s="20"/>
+      <c r="O4" s="20"/>
+      <c r="P4" s="21"/>
+      <c r="Q4" s="21"/>
+      <c r="R4" s="21"/>
+      <c r="S4" s="21"/>
+      <c r="T4" s="20"/>
+      <c r="U4" s="20"/>
+      <c r="V4" s="20"/>
+      <c r="W4" s="20"/>
+      <c r="X4" s="24"/>
+    </row>
+    <row r="5" spans="1:25" s="25" customFormat="1" ht="19" hidden="1" customHeight="1">
       <c r="A5" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="26" t="s">
+      <c r="B5" s="25" t="s">
         <v>35</v>
       </c>
       <c r="C5" s="5">
@@ -3708,25 +3708,25 @@
         <v>334</v>
       </c>
       <c r="E5" s="6"/>
-      <c r="F5" s="27">
+      <c r="F5" s="26">
         <v>-12.69065975</v>
       </c>
-      <c r="G5" s="27">
+      <c r="G5" s="26">
         <v>-5.4230934299999998</v>
       </c>
-      <c r="H5" s="27">
+      <c r="H5" s="26">
         <v>-0.70495701</v>
       </c>
-      <c r="I5" s="27">
+      <c r="I5" s="26">
         <v>0.60290829999999995</v>
       </c>
       <c r="J5" s="7">
         <v>-0.63559155000000001</v>
       </c>
-      <c r="K5" s="27">
+      <c r="K5" s="26">
         <v>-0.39466126000000001</v>
       </c>
-      <c r="L5" s="27"/>
+      <c r="L5" s="26"/>
       <c r="N5" s="4">
         <v>-6.8361689999999996E-3</v>
       </c>
@@ -3741,468 +3741,468 @@
       <c r="U5" s="4"/>
       <c r="V5" s="4"/>
       <c r="W5" s="4"/>
-      <c r="X5" s="28"/>
+      <c r="X5" s="27"/>
     </row>
     <row r="6" spans="1:25">
-      <c r="A6" s="29" t="s">
+      <c r="A6" s="28" t="s">
         <v>75</v>
       </c>
-      <c r="D6" s="32">
+      <c r="D6" s="31">
         <v>385</v>
       </c>
-      <c r="F6" s="27"/>
-      <c r="G6" s="27"/>
-      <c r="H6" s="27"/>
-      <c r="I6" s="27"/>
-      <c r="J6" s="27"/>
-      <c r="K6" s="27"/>
-      <c r="L6" s="27"/>
-      <c r="N6" s="27"/>
-      <c r="O6" s="27"/>
-    </row>
-    <row r="7" spans="1:25" s="27" customFormat="1" ht="24" customHeight="1">
-      <c r="A7" s="37" t="s">
+      <c r="F6" s="26"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="26"/>
+      <c r="I6" s="26"/>
+      <c r="J6" s="26"/>
+      <c r="K6" s="26"/>
+      <c r="L6" s="26"/>
+      <c r="N6" s="26"/>
+      <c r="O6" s="26"/>
+    </row>
+    <row r="7" spans="1:25" s="26" customFormat="1" ht="24" customHeight="1">
+      <c r="A7" s="53" t="s">
         <v>77</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="31">
+      <c r="C7" s="30">
         <v>0.29559999999999997</v>
       </c>
-      <c r="D7" s="32">
+      <c r="D7" s="31">
         <f>C7*$D$6</f>
         <v>113.80599999999998</v>
       </c>
-      <c r="E7" s="27" t="s">
+      <c r="E7" s="26" t="s">
         <v>102</v>
       </c>
-      <c r="F7" s="27">
+      <c r="F7" s="26">
         <v>-2.1306720000000001</v>
       </c>
-      <c r="G7" s="27">
+      <c r="G7" s="26">
         <v>-0.15268522000000001</v>
       </c>
-      <c r="H7" s="43">
+      <c r="H7" s="39">
         <v>1.8632242999999999</v>
       </c>
-      <c r="I7" s="43">
+      <c r="I7" s="39">
         <v>-0.32716109999999998</v>
       </c>
-      <c r="J7" s="27">
+      <c r="J7" s="26">
         <v>-0.48290870000000002</v>
       </c>
-      <c r="K7" s="52">
+      <c r="K7" s="48">
         <v>-0.49344599</v>
       </c>
-      <c r="M7" s="43">
+      <c r="M7" s="39">
         <v>8.2179490000000008</v>
       </c>
-      <c r="N7" s="43">
+      <c r="N7" s="39">
         <v>0.39486012999999998</v>
       </c>
-      <c r="O7" s="43">
+      <c r="O7" s="39">
         <v>0.156967</v>
       </c>
-      <c r="P7" s="44">
+      <c r="P7" s="40">
         <v>0.82051280000000004</v>
       </c>
-      <c r="Q7" s="44">
+      <c r="Q7" s="40">
         <v>0.2991453</v>
       </c>
-      <c r="R7" s="44">
+      <c r="R7" s="40">
         <v>0.41880339999999999</v>
       </c>
-      <c r="S7" s="44">
+      <c r="S7" s="40">
         <v>0.3162393</v>
       </c>
-      <c r="T7" s="43">
+      <c r="T7" s="39">
         <v>3.7350430000000001</v>
       </c>
-      <c r="U7" s="43">
+      <c r="U7" s="39">
         <v>3.1196579999999998</v>
       </c>
-      <c r="V7" s="43">
+      <c r="V7" s="39">
         <v>21794.87</v>
       </c>
-      <c r="W7" s="43">
+      <c r="W7" s="39">
         <v>2.4358970000000002</v>
       </c>
-      <c r="X7" s="38"/>
-    </row>
-    <row r="8" spans="1:25" s="27" customFormat="1" ht="24" customHeight="1">
-      <c r="A8" s="37"/>
+      <c r="X7" s="36"/>
+    </row>
+    <row r="8" spans="1:25" s="26" customFormat="1" ht="24" customHeight="1">
+      <c r="A8" s="53"/>
       <c r="B8" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="31">
+      <c r="C8" s="30">
         <v>0.2422</v>
       </c>
-      <c r="D8" s="32">
+      <c r="D8" s="31">
         <f t="shared" ref="D8:D9" si="0">C8*$D$6</f>
         <v>93.247</v>
       </c>
-      <c r="E8" s="41" t="s">
+      <c r="E8" s="37" t="s">
         <v>78</v>
       </c>
-      <c r="F8" s="52">
+      <c r="F8" s="48">
         <v>1.4358040000000001</v>
       </c>
-      <c r="G8" s="52">
+      <c r="G8" s="48">
         <v>-0.31479732999999999</v>
       </c>
-      <c r="H8" s="43">
+      <c r="H8" s="39">
         <v>1.5521449</v>
       </c>
-      <c r="I8" s="43">
+      <c r="I8" s="39">
         <v>-0.43615769999999998</v>
       </c>
-      <c r="J8" s="52">
+      <c r="J8" s="48">
         <v>-0.59155340000000001</v>
       </c>
-      <c r="K8" s="27">
+      <c r="K8" s="26">
         <v>-1.37762239</v>
       </c>
-      <c r="M8" s="43">
+      <c r="M8" s="39">
         <v>5.6978020000000003</v>
       </c>
-      <c r="N8" s="43">
+      <c r="N8" s="39">
         <v>-0.77384269000000006</v>
       </c>
-      <c r="O8" s="43">
+      <c r="O8" s="39">
         <v>0.24290220000000001</v>
       </c>
-      <c r="P8" s="44">
+      <c r="P8" s="40">
         <v>0.6593407</v>
       </c>
-      <c r="Q8" s="44">
+      <c r="Q8" s="40">
         <v>0.17582420000000001</v>
       </c>
-      <c r="R8" s="44">
+      <c r="R8" s="40">
         <v>0.3626374</v>
       </c>
-      <c r="S8" s="44">
+      <c r="S8" s="40">
         <v>0.21978020000000001</v>
       </c>
-      <c r="T8" s="43">
+      <c r="T8" s="39">
         <v>2.8351649999999999</v>
       </c>
-      <c r="U8" s="43">
+      <c r="U8" s="39">
         <v>3.461538</v>
       </c>
-      <c r="V8" s="43">
+      <c r="V8" s="39">
         <v>19175.82</v>
       </c>
-      <c r="W8" s="43">
+      <c r="W8" s="39">
         <v>1.659341</v>
       </c>
-      <c r="X8" s="38"/>
-      <c r="Y8" s="39"/>
-    </row>
-    <row r="9" spans="1:25" s="27" customFormat="1" ht="24" customHeight="1">
-      <c r="A9" s="37"/>
+      <c r="X8" s="36"/>
+      <c r="Y8" s="51"/>
+    </row>
+    <row r="9" spans="1:25" s="26" customFormat="1" ht="24" customHeight="1">
+      <c r="A9" s="53"/>
       <c r="B9" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C9" s="31">
+      <c r="C9" s="30">
         <v>0.4622</v>
       </c>
-      <c r="D9" s="32">
+      <c r="D9" s="31">
         <f t="shared" si="0"/>
         <v>177.947</v>
       </c>
-      <c r="E9" s="27" t="s">
+      <c r="E9" s="26" t="s">
         <v>103</v>
       </c>
-      <c r="F9" s="27">
+      <c r="F9" s="26">
         <v>-7.940671</v>
       </c>
-      <c r="G9" s="52">
+      <c r="G9" s="48">
         <v>-5.2299619999999998E-2</v>
       </c>
-      <c r="H9" s="53">
+      <c r="H9" s="49">
         <v>-0.22265760000000001</v>
       </c>
-      <c r="I9" s="43">
+      <c r="I9" s="39">
         <v>-0.30412990000000001</v>
       </c>
-      <c r="J9" s="53">
+      <c r="J9" s="49">
         <v>-0.2394645</v>
       </c>
-      <c r="K9" s="53">
+      <c r="K9" s="49">
         <v>6.4262420000000001E-2</v>
       </c>
-      <c r="M9" s="43">
+      <c r="M9" s="39">
         <v>6.0141239999999998</v>
       </c>
-      <c r="N9" s="43">
+      <c r="N9" s="39">
         <v>3.4750980000000001E-2</v>
       </c>
-      <c r="O9" s="43">
+      <c r="O9" s="39">
         <v>-0.46104410000000001</v>
       </c>
-      <c r="P9" s="44">
+      <c r="P9" s="40">
         <v>0.58757060000000005</v>
       </c>
-      <c r="Q9" s="44">
+      <c r="Q9" s="40">
         <v>0.1242938</v>
       </c>
-      <c r="R9" s="44">
+      <c r="R9" s="40">
         <v>0.37853110000000001</v>
       </c>
-      <c r="S9" s="44">
+      <c r="S9" s="40">
         <v>0.38418079999999999</v>
       </c>
-      <c r="T9" s="43">
+      <c r="T9" s="39">
         <v>3.3220339999999999</v>
       </c>
-      <c r="U9" s="43">
+      <c r="U9" s="39">
         <v>3.0677970000000001</v>
       </c>
-      <c r="V9" s="43">
+      <c r="V9" s="39">
         <v>22542.37</v>
       </c>
-      <c r="W9" s="43">
+      <c r="W9" s="39">
         <v>2.3785310000000002</v>
       </c>
-      <c r="X9" s="38"/>
-      <c r="Y9" s="39"/>
+      <c r="X9" s="36"/>
+      <c r="Y9" s="51"/>
     </row>
     <row r="11" spans="1:25">
-      <c r="A11" s="29" t="s">
+      <c r="A11" s="28" t="s">
         <v>76</v>
       </c>
-      <c r="D11" s="32">
+      <c r="D11" s="31">
         <v>463</v>
       </c>
-      <c r="N11" s="45"/>
-      <c r="O11" s="45"/>
-      <c r="P11" s="46"/>
-      <c r="Q11" s="46"/>
-      <c r="R11" s="46"/>
-      <c r="S11" s="46"/>
-      <c r="T11" s="47"/>
-      <c r="U11" s="47"/>
-      <c r="V11" s="47"/>
+      <c r="N11" s="41"/>
+      <c r="O11" s="41"/>
+      <c r="P11" s="42"/>
+      <c r="Q11" s="42"/>
+      <c r="R11" s="42"/>
+      <c r="S11" s="42"/>
+      <c r="T11" s="43"/>
+      <c r="U11" s="43"/>
+      <c r="V11" s="43"/>
       <c r="W11" s="3"/>
     </row>
     <row r="12" spans="1:25" ht="17">
-      <c r="A12" s="40" t="s">
+      <c r="A12" s="50" t="s">
         <v>77</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C12" s="34">
+      <c r="C12" s="33">
         <v>0.25390000000000001</v>
       </c>
-      <c r="D12" s="32">
+      <c r="D12" s="31">
         <f>$D$11*C12</f>
         <v>117.5557</v>
       </c>
-      <c r="E12" s="30" t="s">
+      <c r="E12" s="29" t="s">
         <v>102</v>
       </c>
-      <c r="F12" s="43">
+      <c r="F12" s="39">
         <v>-4.9529459999999998</v>
       </c>
-      <c r="G12" s="43">
+      <c r="G12" s="39">
         <v>-0.24239759999999999</v>
       </c>
-      <c r="H12" s="27">
+      <c r="H12" s="26">
         <v>0.89128750000000001</v>
       </c>
-      <c r="I12" s="27">
+      <c r="I12" s="26">
         <v>-0.63431070000000001</v>
       </c>
-      <c r="J12" s="27">
+      <c r="J12" s="26">
         <v>-0.34457719999999997</v>
       </c>
-      <c r="K12" s="27">
+      <c r="K12" s="26">
         <v>-0.28149000000000002</v>
       </c>
-      <c r="L12" s="45"/>
-      <c r="M12" s="43">
+      <c r="L12" s="41"/>
+      <c r="M12" s="39">
         <v>8.4637309999999992</v>
       </c>
-      <c r="N12" s="43">
+      <c r="N12" s="39">
         <v>0.40352199999999999</v>
       </c>
-      <c r="O12" s="43">
+      <c r="O12" s="39">
         <v>5.6274570000000003E-2</v>
       </c>
-      <c r="P12" s="44">
+      <c r="P12" s="40">
         <v>0.7564767</v>
       </c>
-      <c r="Q12" s="44">
+      <c r="Q12" s="40">
         <v>0.2279793</v>
       </c>
-      <c r="R12" s="44">
+      <c r="R12" s="40">
         <v>0.46113989999999999</v>
       </c>
-      <c r="S12" s="44">
+      <c r="S12" s="40">
         <v>0.37305700000000003</v>
       </c>
-      <c r="T12" s="43">
+      <c r="T12" s="39">
         <v>3.5751300000000001</v>
       </c>
-      <c r="U12" s="43">
+      <c r="U12" s="39">
         <v>3.15544</v>
       </c>
-      <c r="V12" s="43">
+      <c r="V12" s="39">
         <v>28860.1</v>
       </c>
-      <c r="W12" s="43">
+      <c r="W12" s="39">
         <v>2.4404149999999998</v>
       </c>
     </row>
     <row r="13" spans="1:25" ht="17">
-      <c r="A13" s="40"/>
+      <c r="A13" s="50"/>
       <c r="B13" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C13" s="34">
+      <c r="C13" s="33">
         <v>0.36349999999999999</v>
       </c>
-      <c r="D13" s="32">
+      <c r="D13" s="31">
         <f t="shared" ref="D13:D14" si="1">$D$11*C13</f>
         <v>168.3005</v>
       </c>
-      <c r="E13" s="41" t="s">
+      <c r="E13" s="37" t="s">
         <v>78</v>
       </c>
-      <c r="F13" s="52">
+      <c r="F13" s="48">
         <v>-1.249835</v>
       </c>
-      <c r="G13" s="27">
+      <c r="G13" s="26">
         <v>-0.46152549999999998</v>
       </c>
-      <c r="H13" s="27">
+      <c r="H13" s="26">
         <v>0.69025060000000005</v>
       </c>
-      <c r="I13" s="27">
+      <c r="I13" s="26">
         <v>-0.41162399999999999</v>
       </c>
-      <c r="J13" s="27">
+      <c r="J13" s="26">
         <v>-0.60337819999999998</v>
       </c>
-      <c r="K13" s="27">
+      <c r="K13" s="26">
         <v>-0.85088699999999995</v>
       </c>
-      <c r="L13" s="45"/>
-      <c r="M13" s="43">
+      <c r="L13" s="41"/>
+      <c r="M13" s="39">
         <v>8.1869569999999996</v>
       </c>
-      <c r="N13" s="43">
+      <c r="N13" s="39">
         <v>-0.61912016999999997</v>
       </c>
-      <c r="O13" s="43">
+      <c r="O13" s="39">
         <v>0.43055870000000002</v>
       </c>
-      <c r="P13" s="44">
+      <c r="P13" s="40">
         <v>0.65217389999999997</v>
       </c>
-      <c r="Q13" s="44">
+      <c r="Q13" s="40">
         <v>0.13913039999999999</v>
       </c>
-      <c r="R13" s="44">
+      <c r="R13" s="40">
         <v>0.3565217</v>
       </c>
-      <c r="S13" s="44">
+      <c r="S13" s="40">
         <v>0.26086959999999998</v>
       </c>
-      <c r="T13" s="43">
+      <c r="T13" s="39">
         <v>3.1652170000000002</v>
       </c>
-      <c r="U13" s="43">
+      <c r="U13" s="39">
         <v>3.6956519999999999</v>
       </c>
-      <c r="V13" s="43">
+      <c r="V13" s="39">
         <v>26130.43</v>
       </c>
-      <c r="W13" s="43">
+      <c r="W13" s="39">
         <v>1.6086959999999999</v>
       </c>
-      <c r="X13" s="15"/>
+      <c r="X13" s="14"/>
     </row>
     <row r="14" spans="1:25" ht="17">
-      <c r="A14" s="40"/>
+      <c r="A14" s="50"/>
       <c r="B14" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C14" s="34">
+      <c r="C14" s="33">
         <v>0.3826</v>
       </c>
-      <c r="D14" s="32">
+      <c r="D14" s="31">
         <f t="shared" si="1"/>
         <v>177.1438</v>
       </c>
-      <c r="E14" s="27" t="s">
+      <c r="E14" s="26" t="s">
         <v>103</v>
       </c>
-      <c r="F14" s="27">
+      <c r="F14" s="26">
         <v>-9.2812099999999997</v>
       </c>
-      <c r="G14" s="52">
+      <c r="G14" s="48">
         <v>-0.20175299999999999</v>
       </c>
-      <c r="H14" s="52">
+      <c r="H14" s="48">
         <v>0.4240931</v>
       </c>
-      <c r="I14" s="27">
+      <c r="I14" s="26">
         <v>-0.20553950000000001</v>
       </c>
-      <c r="J14" s="27">
+      <c r="J14" s="26">
         <v>-0.86889289999999997</v>
       </c>
-      <c r="K14" s="27">
+      <c r="K14" s="26">
         <v>-0.8099537</v>
       </c>
-      <c r="M14" s="43">
+      <c r="M14" s="39">
         <v>7.0806449999999996</v>
       </c>
-      <c r="N14" s="43">
+      <c r="N14" s="39">
         <v>4.8033859999999998E-2</v>
       </c>
-      <c r="O14" s="43">
+      <c r="O14" s="39">
         <v>-0.21929004999999999</v>
       </c>
-      <c r="P14" s="44">
+      <c r="P14" s="40">
         <v>0.63870970000000005</v>
       </c>
-      <c r="Q14" s="44">
+      <c r="Q14" s="40">
         <v>0.2451613</v>
       </c>
-      <c r="R14" s="44">
+      <c r="R14" s="40">
         <v>0.40645160000000002</v>
       </c>
-      <c r="S14" s="44">
+      <c r="S14" s="40">
         <v>0.27741939999999998</v>
       </c>
-      <c r="T14" s="43">
+      <c r="T14" s="39">
         <v>3.2012990000000001</v>
       </c>
-      <c r="U14" s="43">
+      <c r="U14" s="39">
         <v>3.077922</v>
       </c>
-      <c r="V14" s="43">
+      <c r="V14" s="39">
         <v>27677.42</v>
       </c>
-      <c r="W14" s="43">
+      <c r="W14" s="39">
         <v>2.3806449999999999</v>
       </c>
-      <c r="X14" s="15"/>
+      <c r="X14" s="14"/>
     </row>
     <row r="15" spans="1:25">
-      <c r="F15" s="27"/>
-      <c r="G15" s="27"/>
-      <c r="H15" s="48"/>
-      <c r="I15" s="27"/>
-      <c r="J15" s="27"/>
-      <c r="K15" s="27"/>
-      <c r="M15" s="15"/>
-      <c r="N15" s="15"/>
-      <c r="O15" s="15"/>
+      <c r="F15" s="26"/>
+      <c r="G15" s="26"/>
+      <c r="H15" s="44"/>
+      <c r="I15" s="26"/>
+      <c r="J15" s="26"/>
+      <c r="K15" s="26"/>
+      <c r="M15" s="14"/>
+      <c r="N15" s="14"/>
+      <c r="O15" s="14"/>
       <c r="P15" s="5"/>
       <c r="Q15" s="5"/>
       <c r="R15" s="5"/>
@@ -4210,14 +4210,14 @@
       <c r="T15" s="4"/>
       <c r="U15" s="4"/>
       <c r="V15" s="4"/>
-      <c r="X15" s="15"/>
-      <c r="Y15" s="15"/>
+      <c r="X15" s="14"/>
+      <c r="Y15" s="14"/>
     </row>
     <row r="16" spans="1:25">
-      <c r="H16" s="49"/>
-      <c r="M16" s="15"/>
-      <c r="N16" s="15"/>
-      <c r="O16" s="15"/>
+      <c r="H16" s="45"/>
+      <c r="M16" s="14"/>
+      <c r="N16" s="14"/>
+      <c r="O16" s="14"/>
       <c r="P16" s="5"/>
       <c r="Q16" s="5"/>
       <c r="R16" s="5"/>
@@ -4225,149 +4225,374 @@
       <c r="T16" s="4"/>
       <c r="U16" s="4"/>
       <c r="V16" s="4"/>
-      <c r="X16" s="15"/>
-      <c r="Y16" s="15"/>
+      <c r="X16" s="14"/>
+      <c r="Y16" s="14"/>
     </row>
     <row r="17" spans="5:25" ht="34">
       <c r="E17" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="H17" s="49"/>
-      <c r="I17" s="50"/>
-      <c r="J17" s="50"/>
-      <c r="K17" s="42"/>
-      <c r="L17" s="42"/>
-      <c r="M17" s="50"/>
-      <c r="N17" s="50"/>
-      <c r="O17" s="50"/>
-      <c r="P17" s="51"/>
-      <c r="Q17" s="51"/>
-      <c r="R17" s="51"/>
-      <c r="S17" s="51"/>
-      <c r="T17" s="42"/>
-      <c r="U17" s="42"/>
-      <c r="V17" s="42"/>
-      <c r="W17" s="42"/>
-      <c r="X17" s="50"/>
-      <c r="Y17" s="15"/>
+      <c r="H17" s="45"/>
+      <c r="I17" s="46"/>
+      <c r="J17" s="46"/>
+      <c r="K17" s="38"/>
+      <c r="L17" s="38"/>
+      <c r="M17" s="46"/>
+      <c r="N17" s="46"/>
+      <c r="O17" s="46"/>
+      <c r="P17" s="47"/>
+      <c r="Q17" s="47"/>
+      <c r="R17" s="47"/>
+      <c r="S17" s="47"/>
+      <c r="T17" s="38"/>
+      <c r="U17" s="38"/>
+      <c r="V17" s="38"/>
+      <c r="W17" s="38"/>
+      <c r="X17" s="46"/>
+      <c r="Y17" s="14"/>
     </row>
     <row r="18" spans="5:25" ht="51">
       <c r="E18" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="I18" s="50"/>
-      <c r="J18" s="50"/>
-      <c r="K18" s="42"/>
-      <c r="L18" s="42"/>
-      <c r="M18" s="50"/>
-      <c r="N18" s="50"/>
-      <c r="O18" s="50"/>
-      <c r="P18" s="51"/>
-      <c r="Q18" s="51"/>
-      <c r="R18" s="51"/>
-      <c r="S18" s="51"/>
-      <c r="T18" s="42"/>
-      <c r="U18" s="42"/>
-      <c r="V18" s="42"/>
-      <c r="W18" s="42"/>
-      <c r="X18" s="50"/>
-      <c r="Y18" s="15"/>
+      <c r="F18" s="26">
+        <f>F7*10</f>
+        <v>-21.306720000000002</v>
+      </c>
+      <c r="G18" s="26">
+        <f t="shared" ref="G18:K18" si="2">G7*10</f>
+        <v>-1.5268522</v>
+      </c>
+      <c r="H18" s="26">
+        <f t="shared" si="2"/>
+        <v>18.632242999999999</v>
+      </c>
+      <c r="I18" s="26">
+        <f t="shared" si="2"/>
+        <v>-3.271611</v>
+      </c>
+      <c r="J18" s="26">
+        <f t="shared" si="2"/>
+        <v>-4.8290870000000004</v>
+      </c>
+      <c r="K18" s="26">
+        <f t="shared" si="2"/>
+        <v>-4.9344599000000002</v>
+      </c>
+      <c r="L18" s="38"/>
+      <c r="M18" s="46"/>
+      <c r="N18" s="46"/>
+      <c r="O18" s="46"/>
+      <c r="P18" s="47"/>
+      <c r="Q18" s="47"/>
+      <c r="R18" s="47"/>
+      <c r="S18" s="47"/>
+      <c r="T18" s="38"/>
+      <c r="U18" s="38"/>
+      <c r="V18" s="38"/>
+      <c r="W18" s="38"/>
+      <c r="X18" s="46"/>
+      <c r="Y18" s="14"/>
     </row>
     <row r="19" spans="5:25">
-      <c r="E19" s="30"/>
-      <c r="F19" s="50"/>
-      <c r="G19" s="50"/>
-      <c r="H19" s="50"/>
-      <c r="I19" s="50"/>
-      <c r="J19" s="50"/>
-      <c r="K19" s="50"/>
-      <c r="L19" s="50"/>
-      <c r="M19" s="50"/>
-      <c r="N19" s="50"/>
-      <c r="O19" s="50"/>
-      <c r="P19" s="51"/>
-      <c r="Q19" s="51"/>
-      <c r="R19" s="44"/>
-      <c r="S19" s="44"/>
-      <c r="T19" s="43"/>
-      <c r="Y19" s="15"/>
+      <c r="E19" s="29"/>
+      <c r="F19" s="26">
+        <f t="shared" ref="F19:K19" si="3">F8*10</f>
+        <v>14.358040000000001</v>
+      </c>
+      <c r="G19" s="26">
+        <f t="shared" si="3"/>
+        <v>-3.1479732999999999</v>
+      </c>
+      <c r="H19" s="26">
+        <f t="shared" si="3"/>
+        <v>15.521449</v>
+      </c>
+      <c r="I19" s="26">
+        <f t="shared" si="3"/>
+        <v>-4.3615769999999996</v>
+      </c>
+      <c r="J19" s="26">
+        <f t="shared" si="3"/>
+        <v>-5.9155340000000001</v>
+      </c>
+      <c r="K19" s="26">
+        <f t="shared" si="3"/>
+        <v>-13.7762239</v>
+      </c>
+      <c r="L19" s="46"/>
+      <c r="M19" s="46"/>
+      <c r="N19" s="46"/>
+      <c r="O19" s="46"/>
+      <c r="P19" s="47"/>
+      <c r="Q19" s="47"/>
+      <c r="R19" s="40"/>
+      <c r="S19" s="40"/>
+      <c r="T19" s="39"/>
+      <c r="Y19" s="14"/>
     </row>
     <row r="20" spans="5:25" ht="51">
       <c r="E20" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="F20" s="50"/>
-      <c r="G20" s="50"/>
-      <c r="H20" s="50"/>
-      <c r="I20" s="50"/>
-      <c r="J20" s="50"/>
-      <c r="K20" s="50"/>
-      <c r="L20" s="50"/>
-      <c r="M20" s="50"/>
-      <c r="N20" s="50"/>
-      <c r="O20" s="50"/>
-      <c r="P20" s="51"/>
-      <c r="Q20" s="51"/>
-      <c r="R20" s="51"/>
-      <c r="S20" s="51"/>
-      <c r="T20" s="42"/>
-      <c r="U20" s="42"/>
-      <c r="V20" s="42"/>
-      <c r="W20" s="42"/>
-      <c r="X20" s="50"/>
-      <c r="Y20" s="50"/>
+      <c r="F20" s="26">
+        <f t="shared" ref="F20:K20" si="4">F9*10</f>
+        <v>-79.406710000000004</v>
+      </c>
+      <c r="G20" s="26">
+        <f t="shared" si="4"/>
+        <v>-0.52299620000000002</v>
+      </c>
+      <c r="H20" s="26">
+        <f t="shared" si="4"/>
+        <v>-2.2265760000000001</v>
+      </c>
+      <c r="I20" s="26">
+        <f t="shared" si="4"/>
+        <v>-3.041299</v>
+      </c>
+      <c r="J20" s="26">
+        <f t="shared" si="4"/>
+        <v>-2.3946450000000001</v>
+      </c>
+      <c r="K20" s="26">
+        <f t="shared" si="4"/>
+        <v>0.64262419999999998</v>
+      </c>
+      <c r="L20" s="46"/>
+      <c r="M20" s="46"/>
+      <c r="N20" s="46"/>
+      <c r="O20" s="46"/>
+      <c r="P20" s="47"/>
+      <c r="Q20" s="47"/>
+      <c r="R20" s="47"/>
+      <c r="S20" s="47"/>
+      <c r="T20" s="38"/>
+      <c r="U20" s="38"/>
+      <c r="V20" s="38"/>
+      <c r="W20" s="38"/>
+      <c r="X20" s="46"/>
+      <c r="Y20" s="46"/>
     </row>
     <row r="21" spans="5:25" ht="51">
       <c r="E21" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="F21" s="15"/>
-      <c r="G21" s="15"/>
-      <c r="M21" s="50"/>
-      <c r="N21" s="50"/>
-      <c r="O21" s="50"/>
-      <c r="P21" s="51"/>
-      <c r="Q21" s="51"/>
-      <c r="R21" s="51"/>
-      <c r="S21" s="51"/>
-      <c r="T21" s="42"/>
-      <c r="U21" s="42"/>
-      <c r="V21" s="42"/>
-      <c r="W21" s="42"/>
-      <c r="X21" s="50"/>
-      <c r="Y21" s="50"/>
+      <c r="F21" s="26">
+        <f t="shared" ref="F21:K21" si="5">F10*10</f>
+        <v>0</v>
+      </c>
+      <c r="G21" s="26">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="H21" s="26">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I21" s="26">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="J21" s="26">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="K21" s="26">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M21" s="46"/>
+      <c r="N21" s="46"/>
+      <c r="O21" s="46"/>
+      <c r="P21" s="47"/>
+      <c r="Q21" s="47"/>
+      <c r="R21" s="47"/>
+      <c r="S21" s="47"/>
+      <c r="T21" s="38"/>
+      <c r="U21" s="38"/>
+      <c r="V21" s="38"/>
+      <c r="W21" s="38"/>
+      <c r="X21" s="46"/>
+      <c r="Y21" s="46"/>
     </row>
     <row r="22" spans="5:25" ht="34">
       <c r="E22" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="F22" s="15"/>
-      <c r="G22" s="15"/>
-      <c r="M22" s="15"/>
-      <c r="N22" s="15"/>
+      <c r="F22" s="26">
+        <f t="shared" ref="F22:K22" si="6">F11*10</f>
+        <v>0</v>
+      </c>
+      <c r="G22" s="26">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="H22" s="26">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="I22" s="26">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="J22" s="26">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="K22" s="26">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="M22" s="14"/>
+      <c r="N22" s="14"/>
     </row>
     <row r="23" spans="5:25">
-      <c r="M23" s="15"/>
-      <c r="N23" s="15"/>
+      <c r="F23" s="26">
+        <f t="shared" ref="F23:K23" si="7">F12*10</f>
+        <v>-49.52946</v>
+      </c>
+      <c r="G23" s="26">
+        <f t="shared" si="7"/>
+        <v>-2.4239759999999997</v>
+      </c>
+      <c r="H23" s="26">
+        <f t="shared" si="7"/>
+        <v>8.9128749999999997</v>
+      </c>
+      <c r="I23" s="26">
+        <f t="shared" si="7"/>
+        <v>-6.3431069999999998</v>
+      </c>
+      <c r="J23" s="26">
+        <f t="shared" si="7"/>
+        <v>-3.4457719999999998</v>
+      </c>
+      <c r="K23" s="26">
+        <f t="shared" si="7"/>
+        <v>-2.8149000000000002</v>
+      </c>
+      <c r="M23" s="14"/>
+      <c r="N23" s="14"/>
     </row>
     <row r="24" spans="5:25">
-      <c r="M24" s="15"/>
-      <c r="N24" s="15"/>
+      <c r="F24" s="26">
+        <f>F13*10</f>
+        <v>-12.49835</v>
+      </c>
+      <c r="G24" s="26">
+        <f t="shared" ref="G24:K24" si="8">G13*10</f>
+        <v>-4.6152549999999994</v>
+      </c>
+      <c r="H24" s="26">
+        <f t="shared" si="8"/>
+        <v>6.9025060000000007</v>
+      </c>
+      <c r="I24" s="26">
+        <f t="shared" si="8"/>
+        <v>-4.1162399999999995</v>
+      </c>
+      <c r="J24" s="26">
+        <f t="shared" si="8"/>
+        <v>-6.0337819999999995</v>
+      </c>
+      <c r="K24" s="26">
+        <f t="shared" si="8"/>
+        <v>-8.5088699999999999</v>
+      </c>
+      <c r="M24" s="14"/>
+      <c r="N24" s="14"/>
     </row>
     <row r="25" spans="5:25">
-      <c r="M25" s="15"/>
-      <c r="N25" s="15"/>
-      <c r="O25" s="15"/>
-      <c r="P25" s="44"/>
-      <c r="Q25" s="44"/>
-      <c r="R25" s="44"/>
-      <c r="S25" s="44"/>
-      <c r="T25" s="43"/>
-      <c r="U25" s="43"/>
-      <c r="V25" s="43"/>
-      <c r="W25" s="43"/>
-      <c r="X25" s="15"/>
-      <c r="Y25" s="15"/>
+      <c r="F25" s="26">
+        <f t="shared" ref="F25:K25" si="9">F14*10</f>
+        <v>-92.812100000000001</v>
+      </c>
+      <c r="G25" s="26">
+        <f t="shared" si="9"/>
+        <v>-2.0175299999999998</v>
+      </c>
+      <c r="H25" s="26">
+        <f t="shared" si="9"/>
+        <v>4.2409309999999998</v>
+      </c>
+      <c r="I25" s="26">
+        <f t="shared" si="9"/>
+        <v>-2.0553950000000003</v>
+      </c>
+      <c r="J25" s="26">
+        <f t="shared" si="9"/>
+        <v>-8.6889289999999999</v>
+      </c>
+      <c r="K25" s="26">
+        <f t="shared" si="9"/>
+        <v>-8.0995369999999998</v>
+      </c>
+      <c r="M25" s="14"/>
+      <c r="N25" s="14"/>
+      <c r="O25" s="14"/>
+      <c r="P25" s="40"/>
+      <c r="Q25" s="40"/>
+      <c r="R25" s="40"/>
+      <c r="S25" s="40"/>
+      <c r="T25" s="39"/>
+      <c r="U25" s="39"/>
+      <c r="V25" s="39"/>
+      <c r="W25" s="39"/>
+      <c r="X25" s="14"/>
+      <c r="Y25" s="14"/>
+    </row>
+    <row r="26" spans="5:25">
+      <c r="F26" s="26">
+        <f t="shared" ref="F26:K26" si="10">F15*10</f>
+        <v>0</v>
+      </c>
+      <c r="G26" s="26">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="H26" s="26">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="I26" s="26">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="J26" s="26">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="K26" s="26">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="5:25">
+      <c r="F27" s="26">
+        <f t="shared" ref="F27:K27" si="11">F16*10</f>
+        <v>0</v>
+      </c>
+      <c r="G27" s="26">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="H27" s="26">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="I27" s="26">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J27" s="26">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="K27" s="26">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="5">
